--- a/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260624.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260624.xlsx
@@ -1063,17 +1063,17 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>華碩</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>55,180,000</t>
+          <t>1,661,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1085,17 +1085,17 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>華碩</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>1,661,000</t>
+          <t>55,180,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -1129,17 +1129,17 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>元大金</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>18,876,648</t>
+          <t>28,448,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -1151,17 +1151,17 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>元大金</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>28,448,000</t>
+          <t>18,876,648</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -1701,17 +1701,17 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2903</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>豐興</t>
+          <t>遠百</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>9,024,000</t>
+          <t>23,417,000</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -1723,17 +1723,17 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>2903</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>遠百</t>
+          <t>豐興</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>23,417,000</t>
+          <t>9,024,000</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -1899,17 +1899,17 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>2883</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>可成</t>
+          <t>凱基金</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>1,742,000</t>
+          <t>12,544,200</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -1921,17 +1921,17 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>2883</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>凱基金</t>
+          <t>可成</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>12,544,200</t>
+          <t>1,742,000</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
